--- a/bov-generator/templates/Comps Blank Template - Briggs.xlsx
+++ b/bov-generator/templates/Comps Blank Template - Briggs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Index" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="On Market" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sold" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Index" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="On Market" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -1216,7 +1216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:W108"/>
+  <dimension ref="A2:W108"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="45" min="1" max="1"/>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="O5" s="92" t="inlineStr">
         <is>
-          <t>RENEWAL OPTIONS</t>
+          <t>OPTIONS</t>
         </is>
       </c>
       <c r="P5" s="92" t="inlineStr">
@@ -6109,7 +6109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AA108"/>
+  <dimension ref="A2:AA108"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="45" min="1" max="1"/>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="O5" s="92" t="inlineStr">
         <is>
-          <t>RENEWAL OPTIONS</t>
+          <t>OPTIONS</t>
         </is>
       </c>
       <c r="P5" s="92" t="inlineStr">
